--- a/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
@@ -420,7 +420,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py IW20760 · 2026-10-20 13:54 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py SR61467 · 2026-10-21 09:57 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>MAX(IFF(surv.LTV_CAP_MONTHS IS NOT NULL, surv.RMST_CUM, NULL))</t>
+          <t>MAX(IFF(surv.LTV_CAP_AVG_ACTIVE_MONTHS IS NOT NULL, surv.RMST_CUM, NULL))</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -14893,7 +14893,7 @@
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>MAX(IFF(surv.LTV_CAP_MONTHS IS NOT NULL, surv.RMST_CUM, NULL))</t>
+          <t>MAX(IFF(surv.LTV_CAP_AVG_ACTIVE_MONTHS IS NOT NULL, surv.RMST_CUM, NULL))</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -15628,7 +15628,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -15717,7 +15717,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>MAX(IFF(surv.LTV_CAP_MONTHS IS NOT NULL, surv.RMST_CUM, NULL))</t>
+          <t>MAX(IFF(surv.LTV_CAP_AVG_ACTIVE_MONTHS IS NOT NULL, surv.RMST_CUM, NULL))</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -16255,7 +16255,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -16437,7 +16437,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -16615,7 +16615,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -16875,7 +16875,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>MAX(IFF(surv.LTV_CAP_MONTHS IS NOT NULL, surv.RMST_CUM, NULL))</t>
+          <t>MAX(IFF(surv.LTV_CAP_AVG_ACTIVE_MONTHS IS NOT NULL, surv.RMST_CUM, NULL))</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -17068,7 +17068,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -17797,7 +17797,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -17954,7 +17954,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>fee.TOTAL_PAID_FEE_BILLABLE·fee.DISTINCT_PAYING_MEMBERS · surv.EXP_TENURE_MONTHS · surv.SURV_LTV_CAP_MONTHS</t>
+          <t>fee.TOTAL_PAID_FEE_BILLABLE·fee.DISTINCT_PAYING_MEMBERS · surv.EXP_TENURE_MONTHS · surv.SURV_LTV_CAP_AVG_ACTIVE_MONTHS</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -18215,7 +18215,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py IW20760 · 2026-10-20 13:54 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py SR61467 · 2026-10-21 09:57 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>

--- a/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
@@ -420,7 +420,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py SR61467 · 2026-10-21 09:57 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py SR61467 · 2026-10-21 10:24 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -18215,7 +18215,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py SR61467 · 2026-10-21 09:57 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py SR61467 · 2026-10-21 10:24 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>

--- a/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
@@ -420,7 +420,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py SR61467 · 2026-10-21 10:24 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-21 13:24 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,11 @@
           <t>BRONZE_AGENCY.DGT_AD_CMPGN_DTLS | BRONZE_AGENCY.REBRDC_AD_CMPGN_DTLS | BRONZE_AGENCY.VIDEO_AD_CMPGN_DTLS | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>필드</t>
@@ -954,7 +958,11 @@
           <t>BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>필드</t>
@@ -1039,7 +1047,11 @@
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>필드</t>
@@ -1234,7 +1246,11 @@
           <t>BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>필드</t>
@@ -2137,7 +2153,11 @@
           <t>BRONZE_AGENCY.DGT_AD_CMPGN_DTLS | BRONZE_AGENCY.REBRDC_AD_CMPGN_DTLS | BRONZE_AGENCY.VIDEO_AD_CMPGN_DTLS | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>필드</t>
@@ -2332,7 +2352,11 @@
           <t>BRONZE_CRM.TM_RM_CHILD_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>필드</t>
@@ -5939,7 +5963,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -5947,7 +5971,11 @@
           <t>BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TH_MM_FDRM_MBER_STNG_DTLS | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R88" t="inlineStr">
         <is>
           <t>필드</t>
@@ -8443,7 +8471,11 @@
           <t>BRONZE_AGENCY.DGT_AD_CMPGN_DTLS | BRONZE_AGENCY.REBRDC_AD_CMPGN_DTLS | BRONZE_AGENCY.VIDEO_AD_CMPGN_DTLS | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R124" t="inlineStr">
         <is>
           <t>필드</t>
@@ -9358,7 +9390,11 @@
           <t>BRONZE_AGENCY.DGT_AD_CMPGN_DTLS | BRONZE_AGENCY.REBRDC_AD_CMPGN_DTLS | BRONZE_AGENCY.VIDEO_AD_CMPGN_DTLS | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="Q135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R135" t="inlineStr">
         <is>
           <t>필드</t>
@@ -10281,7 +10317,11 @@
           <t>BRONZE_AGENCY.DGT_AD_CMPGN_DTLS | BRONZE_AGENCY.REBRDC_AD_CMPGN_DTLS | BRONZE_AGENCY.VIDEO_AD_CMPGN_DTLS | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="Q146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R146" t="inlineStr">
         <is>
           <t>필드</t>
@@ -10362,7 +10402,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -10370,7 +10410,11 @@
           <t>BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TH_MM_FDRM_MBER_STNG_DTLS | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R147" t="inlineStr">
         <is>
           <t>필드</t>
@@ -11240,7 +11284,11 @@
           <t>BRONZE_AGENCY.DGT_AD_CMPGN_DTLS | BRONZE_AGENCY.REBRDC_AD_CMPGN_DTLS | BRONZE_AGENCY.VIDEO_AD_CMPGN_DTLS | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="Q157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R157" t="inlineStr">
         <is>
           <t>필드</t>
@@ -11422,7 +11470,11 @@
           <t>BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
-      <c r="Q159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R159" t="inlineStr">
         <is>
           <t>필드</t>
@@ -12207,7 +12259,11 @@
           <t>BRONZE_AGENCY.DGT_AD_CMPGN_DTLS | BRONZE_AGENCY.REBRDC_AD_CMPGN_DTLS | BRONZE_AGENCY.VIDEO_AD_CMPGN_DTLS | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="Q168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R168" t="inlineStr">
         <is>
           <t>필드</t>
@@ -12890,7 +12946,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -12898,7 +12954,11 @@
           <t>BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TH_MM_FDRM_MBER_STNG_DTLS | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="Q179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R179" t="inlineStr">
         <is>
           <t>필드</t>
@@ -12987,7 +13047,11 @@
           <t>BRONZE_AGENCY.DGT_AD_CMPGN_DTLS | BRONZE_AGENCY.REBRDC_AD_CMPGN_DTLS | BRONZE_AGENCY.VIDEO_AD_CMPGN_DTLS | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG</t>
         </is>
       </c>
-      <c r="Q180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R180" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15450,7 +15514,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -15458,7 +15522,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R207" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15539,7 +15607,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -15547,7 +15615,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R208" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15628,7 +15700,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -15636,7 +15708,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R209" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15717,7 +15793,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -15725,7 +15801,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R210" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15806,7 +15886,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -15814,7 +15894,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R211" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15988,7 +16072,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -15996,7 +16080,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R213" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16077,7 +16165,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -16085,7 +16173,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R214" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16166,7 +16258,7 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -16174,7 +16266,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R215" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16255,7 +16351,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -16263,7 +16359,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R216" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16437,7 +16537,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -16445,7 +16545,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R218" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16526,7 +16630,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -16534,7 +16638,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R219" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16615,7 +16723,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -16623,7 +16731,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R220" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16704,7 +16816,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -16712,7 +16824,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R221" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16979,7 +17095,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -16987,7 +17103,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R224" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17068,7 +17188,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -17076,7 +17196,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R225" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17157,7 +17281,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -17165,7 +17289,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R226" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17246,7 +17374,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -17254,7 +17382,11 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R227" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17797,7 +17929,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -17805,7 +17937,11 @@
           <t>BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TH_MM_FDRM_MBER_STNG_DTLS | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="Q234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>?.CRM_HOLIDAY</t>
+        </is>
+      </c>
       <c r="R234" t="inlineStr">
         <is>
           <t>필드</t>
@@ -18215,7 +18351,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py SR61467 · 2026-10-21 10:24 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-21 13:24 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>

--- a/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
@@ -420,7 +420,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-21 13:24 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_DEV_TARGET | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_DEV_TARGET | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>SILVER.CRM_ORG</t>
+          <t>SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>SILVER.CRM_BIZ_TARGET | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_ORG | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_BIZ_TARGET | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_SPONSORSHIP | SILVER.MAP_BUDGET_PROCEDURE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>SILVER.CRM_BIZ_TARGET | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_ORG | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_BIZ_TARGET | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_SPONSORSHIP | SILVER.MAP_BUDGET_PROCEDURE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -5971,11 +5971,7 @@
           <t>BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TH_MM_FDRM_MBER_STNG_DTLS | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
           <t>필드</t>
@@ -6166,7 +6162,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_DEV_TARGET | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_DEV_TARGET | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -6825,7 +6821,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_DEV_TARGET | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_DEV_TARGET | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -6914,7 +6910,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -7255,7 +7251,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -7348,7 +7344,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -7441,7 +7437,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -7534,7 +7530,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -8038,7 +8034,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -8131,7 +8127,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -8224,7 +8220,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -8370,7 +8366,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -8609,7 +8605,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -8702,7 +8698,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -8848,7 +8844,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -8941,7 +8937,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -9034,7 +9030,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -9127,7 +9123,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -9216,7 +9212,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -9552,7 +9548,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -9645,7 +9641,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -9738,7 +9734,7 @@
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -9831,7 +9827,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -9924,7 +9920,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -10070,7 +10066,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -10163,7 +10159,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -10402,7 +10398,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -10410,11 +10406,7 @@
           <t>BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TH_MM_FDRM_MBER_STNG_DTLS | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q147" t="inlineStr"/>
       <c r="R147" t="inlineStr">
         <is>
           <t>필드</t>
@@ -10548,7 +10540,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -10637,7 +10629,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -10726,7 +10718,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -10815,7 +10807,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -10908,7 +10900,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -11001,7 +10993,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -11094,7 +11086,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -11183,7 +11175,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -11373,7 +11365,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -11648,7 +11640,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -11741,7 +11733,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P162" t="inlineStr">
@@ -11829,12 +11821,12 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -11918,12 +11910,12 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -12007,12 +11999,12 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -12100,12 +12092,12 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -12343,12 +12335,12 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -12946,7 +12938,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -12954,11 +12946,7 @@
           <t>BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TH_MM_FDRM_MBER_STNG_DTLS | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="Q179" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q179" t="inlineStr"/>
       <c r="R179" t="inlineStr">
         <is>
           <t>필드</t>
@@ -13132,7 +13120,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>SILVER.ERP_BUDGET</t>
+          <t>SILVER.ERP_BUDGET | SILVER.MAP_BUDGET_PROCEDURE</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -13221,7 +13209,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -13314,7 +13302,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -13403,7 +13391,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -13496,7 +13484,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -13589,7 +13577,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -13682,7 +13670,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -13775,7 +13763,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -13864,7 +13852,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -13957,7 +13945,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -14050,7 +14038,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -14143,7 +14131,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -14236,7 +14224,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -14329,7 +14317,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -14422,7 +14410,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -14515,7 +14503,7 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -14604,7 +14592,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -14697,7 +14685,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -14790,7 +14778,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -14879,7 +14867,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -14972,7 +14960,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -15056,12 +15044,12 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -15145,12 +15133,12 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -15238,12 +15226,12 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -15327,12 +15315,12 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -15420,12 +15408,12 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -15509,12 +15497,12 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -15522,11 +15510,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q207" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15602,12 +15586,12 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -15615,11 +15599,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q208" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15695,12 +15675,12 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -15708,11 +15688,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q209" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15788,12 +15764,12 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -15801,11 +15777,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q210" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15881,12 +15853,12 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -15894,11 +15866,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q211" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15983,7 +15951,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -16067,12 +16035,12 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -16080,11 +16048,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16160,12 +16124,12 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -16173,11 +16137,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q214" t="inlineStr"/>
       <c r="R214" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16253,12 +16213,12 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -16266,11 +16226,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16346,12 +16302,12 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -16359,11 +16315,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16443,12 +16395,12 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -16532,12 +16484,12 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -16545,11 +16497,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q218" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16625,12 +16573,12 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -16638,11 +16586,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q219" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16718,12 +16662,12 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -16731,11 +16675,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q220" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16811,12 +16751,12 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -16824,11 +16764,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q221" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16908,12 +16844,12 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -17006,7 +16942,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -17090,12 +17026,12 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -17103,11 +17039,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q224" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17183,12 +17115,12 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -17196,11 +17128,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q225" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17276,12 +17204,12 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -17289,11 +17217,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17369,12 +17293,12 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SEND_TYPE | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -17382,11 +17306,7 @@
           <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
-      <c r="Q227" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17751,7 +17671,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P232" t="inlineStr">
@@ -17840,7 +17760,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -17929,7 +17849,7 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP</t>
+          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MEMBER_STATUS_HIST | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_SPONSORSHIP | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -17937,11 +17857,7 @@
           <t>BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TH_MM_FDRM_MBER_STNG_DTLS | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO</t>
         </is>
       </c>
-      <c r="Q234" t="inlineStr">
-        <is>
-          <t>?.CRM_HOLIDAY</t>
-        </is>
-      </c>
+      <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr">
         <is>
           <t>필드</t>
@@ -18022,7 +17938,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>SILVER.ERP_BUDGET</t>
+          <t>SILVER.ERP_BUDGET | SILVER.MAP_BUDGET_PROCEDURE</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -18351,7 +18267,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-21 13:24 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>

--- a/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
@@ -420,7 +420,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -11826,15 +11826,19 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R163" t="inlineStr">
         <is>
           <t>필드</t>
@@ -11915,15 +11919,19 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q164" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R164" t="inlineStr">
         <is>
           <t>필드</t>
@@ -12004,15 +12012,19 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q165" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R165" t="inlineStr">
         <is>
           <t>필드</t>
@@ -12097,15 +12109,19 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R166" t="inlineStr">
         <is>
           <t>필드</t>
@@ -12340,15 +12356,19 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R169" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15049,15 +15069,19 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q202" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R202" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15138,15 +15162,19 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q203" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R203" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15231,15 +15259,19 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q204" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R204" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15320,15 +15352,19 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q205" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R205" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15413,15 +15449,19 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q206" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R206" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15502,15 +15542,19 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q207" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R207" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15591,15 +15635,19 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q208" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R208" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15680,15 +15728,19 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q209" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R209" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15769,15 +15821,19 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q210" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R210" t="inlineStr">
         <is>
           <t>필드</t>
@@ -15858,15 +15914,19 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q211" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R211" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16040,15 +16100,19 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q213" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R213" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16129,15 +16193,19 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q214" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R214" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16218,15 +16286,19 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q215" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R215" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16307,15 +16379,19 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q216" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R216" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16400,15 +16476,19 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q217" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R217" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16489,15 +16569,19 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q218" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R218" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16578,15 +16662,19 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q219" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R219" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16667,15 +16755,19 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q220" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R220" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16756,15 +16848,19 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q221" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R221" t="inlineStr">
         <is>
           <t>필드</t>
@@ -16849,15 +16945,19 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q222" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R222" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17031,15 +17131,19 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q224" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R224" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17120,15 +17224,19 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q225" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R225" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17209,15 +17317,19 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q226" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R226" t="inlineStr">
         <is>
           <t>필드</t>
@@ -17298,15 +17410,19 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
-      <c r="Q227" t="inlineStr"/>
+          <t>BRONZE_CRM.SND_MEMBER_LIST | BRONZE_CRM.SND_MEMBER_OPEN_LOG | BRONZE_CRM.SND_REQ_MST | BRONZE_CRM.TC_CMMN_CD | BRONZE_CRM.TC_CMMN_DTL_CD | BRONZE_CRM.TC_MKTNG_DTL_CD | BRONZE_CRM.TD_MS_AT_TMPLAT_BTN_LIST | BRONZE_CRM.TD_MS_CRMN_PRTCPNT | BRONZE_CRM.TD_MS_EMAIL_LQY_SNDNG | BRONZE_CRM.TD_MS_EMAIL_SNDNG_DTLS | BRONZE_CRM.TD_MS_EVENT_PRTCPNT_DTL | BRONZE_CRM.TD_MS_MSG_AT_LQY_SNDNG | BRONZE_CRM.TD_MS_MSG_AT_SNDNG_DTLS | BRONZE_CRM.TD_MS_PSTMTR_LQY_SNDNG | BRONZE_CRM.TD_MS_PSTMTR_SNDNG_DTL | BRONZE_CRM.TM_CM_BRND_MNG | BRONZE_CRM.TM_CM_CMPGN_MNG | BRONZE_CRM.TM_CM_DEPT_INFO | BRONZE_CRM.TM_CM_SCHDUL_MNG | BRONZE_CRM.TM_CM_SPNSR_BSNS_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_DVLP_AMT | BRONZE_CRM.TM_MM_FDRM_MBER_INFO | BRONZE_CRM.TM_MM_FDRM_MBER_IRSD | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_BSNS | BRONZE_CRM.TM_MM_FDRM_MBER_SPNSR_DSCNTC | BRONZE_CRM.TM_MM_ONCE_MBER_INFO | BRONZE_CRM.TM_MS_AT_TMPLAT_MNG | BRONZE_CRM.TM_MS_CRMN | BRONZE_CRM.TM_MS_EMAIL_SNDNG | BRONZE_CRM.TM_MS_EMAIL_TMPLAT_MNG | BRONZE_CRM.TM_MS_EVENT | BRONZE_CRM.TM_MS_MSG_AT_SNDNG | BRONZE_CRM.TM_MS_PSTMTR_SNDNG | BRONZE_CRM.TM_PM_DNTN_DTLS | BRONZE_CRM.TM_PM_MBRFEE_ACMSLT | BRONZE_CRM.TM_PM_SETLE_INFO | BRONZE_CRM.TM_RM_RELATNSP_GFTMNEY_INFO | BRONZE_CRM.TM_RM_RELATNSP_LETTER_INFO | BRONZE_CRM.TM_RM_RELATNSP_MSTR_INFO</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+        </is>
+      </c>
       <c r="R227" t="inlineStr">
         <is>
           <t>필드</t>
@@ -18267,7 +18383,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-27 13:14 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>

--- a/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
+++ b/85_실제 인수인계 문서/20_정식산출물/N03_통합데이터사전.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S239"/>
+  <dimension ref="A1:S246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-31 09:45 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MARKETING|MEMBER|EXECUTIVE</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MARKETING|MEMBER|EXECUTIVE</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>MARKETING|MEMBER|EXECUTIVE</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>MARKETING|MEMBER|EXECUTIVE</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>MARKETING|MEMBER|EXECUTIVE</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>MARKETING|MEMBER|EXECUTIVE</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -11836,7 +11836,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R163" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R164" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
@@ -12104,12 +12104,12 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -12119,7 +12119,7 @@
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>MARKETING|MEMBER|EXECUTIVE</t>
+          <t>MARKETING</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -12351,12 +12351,12 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
@@ -15064,12 +15064,12 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R202" t="inlineStr">
@@ -15157,12 +15157,12 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -15172,7 +15172,7 @@
       </c>
       <c r="Q203" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R203" t="inlineStr">
@@ -15254,12 +15254,12 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -15269,7 +15269,7 @@
       </c>
       <c r="Q204" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R204" t="inlineStr">
@@ -15347,12 +15347,12 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="Q205" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R205" t="inlineStr">
@@ -15444,12 +15444,12 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="Q206" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R206" t="inlineStr">
@@ -15537,12 +15537,12 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="Q207" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R207" t="inlineStr">
@@ -15630,12 +15630,12 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="Q208" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R208" t="inlineStr">
@@ -15723,12 +15723,12 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="Q209" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R209" t="inlineStr">
@@ -15816,12 +15816,12 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -15831,7 +15831,7 @@
       </c>
       <c r="Q210" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R210" t="inlineStr">
@@ -15909,12 +15909,12 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="Q211" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R211" t="inlineStr">
@@ -16095,12 +16095,12 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="Q213" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R213" t="inlineStr">
@@ -16188,12 +16188,12 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -16203,7 +16203,7 @@
       </c>
       <c r="Q214" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
@@ -16281,12 +16281,12 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -16296,7 +16296,7 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
@@ -16374,12 +16374,12 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R216" t="inlineStr">
@@ -16471,12 +16471,12 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R217" t="inlineStr">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R218" t="inlineStr">
@@ -16657,12 +16657,12 @@
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -16672,7 +16672,7 @@
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R219" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -16765,7 +16765,7 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R220" t="inlineStr">
@@ -16843,12 +16843,12 @@
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -16858,7 +16858,7 @@
       </c>
       <c r="Q221" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R221" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_ORG | GOLD.DIM_REASON | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MESSAGE_DISPATCH</t>
         </is>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="Q222" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R222" t="inlineStr">
@@ -17126,12 +17126,12 @@
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R224" t="inlineStr">
@@ -17219,12 +17219,12 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R225" t="inlineStr">
@@ -17312,12 +17312,12 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -17327,7 +17327,7 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R226" t="inlineStr">
@@ -17405,12 +17405,12 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
+          <t>GOLD.DIM_CAMPAIGN | GOLD.DIM_DATE | GOLD.DIM_EVENT | GOLD.DIM_MARKETING_CAMPAIGN | GOLD.DIM_MEMBER_ACQUISITION | GOLD.DIM_ORG | GOLD.DIM_PAYMENT | GOLD.DIM_REASON | GOLD.DIM_SEND_REQUEST | GOLD.DIM_SPONSORSHIP | GOLD.FACT_AT_GA_CLICK | GOLD.FACT_AT_GA_LINK_MAP | GOLD.FACT_EVENT_ATTENDANCE | GOLD.FACT_MEMBER_COHORT | GOLD.FACT_MEMBER_EVENT | GOLD.FACT_MEMBER_FEE | GOLD.FACT_MEMBER_MONTHLY | GOLD.FACT_MEMBER_SPONSORSHIP_SPAN | GOLD.FACT_MESSAGE_DISPATCH | GOLD.WIDE_MEMBER_SERVICE_COHORT</t>
         </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
+          <t>SILVER.BIGQUERY_BASIC | SILVER.BIGQUERY_EVENT | SILVER.BIGQUERY_REFINED_DATA | SILVER.CRM_CAMPAIGN | SILVER.CRM_CODE | SILVER.CRM_CODE_GROUP | SILVER.CRM_EVENT | SILVER.CRM_EVENT_PARTICIPATION | SILVER.CRM_HOLIDAY | SILVER.CRM_MARKETING_CAMPAIGN | SILVER.CRM_MEMBER | SILVER.CRM_MEMBER_AMT_CHANGE | SILVER.CRM_MEMBER_DEV | SILVER.CRM_MEMBER_DISCONTINUE | SILVER.CRM_MEMBER_SPONSOR_BIZ | SILVER.CRM_MEMBER_SPONSOR_SPAN | SILVER.CRM_MSG_TEMPLATE | SILVER.CRM_MSG_TEMPLATE_BUTTON | SILVER.CRM_ORG | SILVER.CRM_ORG_CLEAN | SILVER.CRM_PAYMENT_BILLING | SILVER.CRM_PAYMENT_METHOD | SILVER.CRM_RELATION_ACTIVITY | SILVER.CRM_SEND_MEMBER | SILVER.CRM_SEND_REQUEST | SILVER.CRM_SEND_RESULT | SILVER.CRM_SPONSORSHIP | SILVER.CRM_SPONSOR_RELATION | SILVER.MAP_AT_GA_LINK | SILVER.MAP_SERVICE_GROUP_RULE | SILVER.MAP_SPONSORSHIP_GROUP4</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -17420,7 +17420,7 @@
       </c>
       <c r="Q227" t="inlineStr">
         <is>
-          <t>?.FACT_AT_GA_CLICK | ?.FACT_AT_GA_LINK_MAP | ?.MAP_AT_GA_LINK | SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
+          <t>SILVER/SILVER_2.BIGQUERY_REFINED_DATA</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
@@ -18363,6 +18363,517 @@
       <c r="S239" t="inlineStr">
         <is>
           <t>사용자 지시 (2026-10-15 · O235) · 신규지표_20260820.csv:29·30 · 03_지표사전 신규.md:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>RT-31</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>최종 광고비(원)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>[개발] 마케팅캠페인별 최종 광고비 — 마케팅 분석 Agent 캠페인 비용표(마케팅캠페인명 · 연월). 세 원천(디지털·영상·방송)의 같은 개념을 합한 현업 확정 정의(데분_6 · O270).</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>최종 광고비 = 디지털 최종정산금액(LAST_STMT_AMT) + 영상 최종광고비(LAST_AD_COST) + 방송 총비용(TOT_COST)</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>(대응 상태 미기재)</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>MARKETING</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>analyst_mktg_campaign_cost</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>mcc.FINAL_AD_COST_SUM · mcc.FINAL_AD_COST_NULL_ROWS_SUM</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>차원·사실</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>필드(base 미해결)</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>마케팅 피드백 3차 데분_2·6 · 현업 확정(O270) · O273 지표사전 등재(O274)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>RT-32</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>디지털 최종정산금액(원)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>[개발] 마케팅캠페인별 디지털 최종정산금액 — 마케팅 분석 Agent 캠페인 비용표(마케팅캠페인명 · 연월).</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>디지털 최종정산금액 = 광고비 + 마크업 + 부가세</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>(대응 상태 미기재)</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>MARKETING</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>analyst_mktg_campaign_cost</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>mcc.AD_SETTLE_AMT</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>차원·사실</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>필드(base 미해결)</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>마케팅 피드백 3차 데분_2·6 · 현업 확정(O270) · O273 지표사전 등재(O274)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>RT-33</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>방송 총비용(방송 최종 광고비 · 원)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>[개발] 마케팅캠페인별 방송(재송출·방송) 최종 광고비 — 마케팅 분석 Agent 캠페인 비용표(마케팅캠페인명 · 연월). 현업 확정(O270).</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>방송 총비용 = 총비용 TOT_COST(편성비 + 콘텐츠구입비 + 콜센터운영비)</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>(대응 상태 미기재)</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>MARKETING</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>analyst_mktg_campaign_cost</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>mcc.FINAL_AD_COST_REBROADCAST_SUM</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>차원·사실</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>필드(base 미해결)</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>마케팅 피드백 3차 데분_2·6 · 현업 확정(O270) · O273 지표사전 등재(O274)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>RT-34</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>캠페인 제작비(원)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>[개발] 마케팅캠페인별 제작비 — 마케팅 분석 Agent 캠페인 비용표(마케팅캠페인명 · 연월). 현업 확정 규칙(데분_2 · O270).</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>제작비 = 지출결의 금액 중 콘텐츠구분자(CONTENTS_DELIMITER = 세부캠페인코드) 기재분 전체</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>(대응 상태 미기재)</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>MARKETING</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>analyst_mktg_campaign_cost</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>mcc.TOTAL_PROD_COST</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>차원·사실</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>필드(base 미해결)</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>마케팅 피드백 3차 데분_2·6 · 현업 확정(O270) · O273 지표사전 등재(O274)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>RT-35</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>CRM 기반 개발(건) — 캠페인 비용표 기본</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>[개발] 마케팅캠페인별 CRM 기반 개발(건) — 마케팅 분석 Agent 캠페인 비용표(마케팅캠페인명 · 연월). 이 표의 개발건수·개발단가 기본 지표(O270-D 사용자 결정).</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>CRM 기반 개발(건) = CRM 개발 사건 금액 ÷ 10000(상계 규칙 적용 · 신규·증액·재후원)</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>(대응 상태 미기재)</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>MARKETING</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>analyst_mktg_campaign_cost</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>mcc.TOTAL_DEV_CNT_CRM</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>차원·사실</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>필드(base 미해결)</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>마케팅 피드백 3차 데분_2·6 · 현업 확정(O270) · O273 지표사전 등재(O274)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>RT-36</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>CRM 개발단가(최종 광고비 기준 · 원/건)</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>[개발] 마케팅캠페인별 CRM 개발단가 — 마케팅 분석 Agent 캠페인 비용표(마케팅캠페인명 · 연월).</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>CRM 개발단가 = 최종 광고비 ÷ CRM 기반 개발(건)</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>(대응 상태 미기재)</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>MARKETING</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>analyst_mktg_campaign_cost</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>mcc.DEV_UNIT_PRICE_CRM</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>차원·사실</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>필드(base 미해결)</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>마케팅 피드백 3차 데분_2·6 · 현업 확정(O270) · O273 지표사전 등재(O274)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>RT-37</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>제작비 포함 개발단가(원/건)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>[개발] 마케팅캠페인별 제작비 포함 개발단가 — 마케팅 분석 Agent 캠페인 비용표(마케팅캠페인명 · 연월).</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>제작비 포함 개발단가 = (광고비 + 제작비) ÷ MSTR 개발(건)</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>(대응 상태 미기재)</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>MARKETING</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>analyst_mktg_campaign_cost</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>MCC</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>mcc.TOTAL_COST_UNIT_PRICE_MSTR</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>차원·사실</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>필드(base 미해결)</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>마케팅 피드백 3차 데분_2·6 · 현업 확정(O270) · O273 지표사전 등재(O274)</t>
         </is>
       </c>
     </row>
@@ -18383,7 +18894,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-31 01:31 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
+          <t># 생성 = scripts/n03_catalog_build.py ZL50263 · 2026-10-31 09:45 KST · 입력 = D01·D09·D08·D06 csv · 손으로 고치지 말 것</t>
         </is>
       </c>
     </row>
@@ -18394,7 +18905,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
@@ -18414,7 +18925,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
